--- a/results0.xlsx
+++ b/results0.xlsx
@@ -1,34 +1,52 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
   <fonts count="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +65,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -199,6 +150,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,6 +185,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -267,20 +220,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -402,174 +351,193 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E8"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Dataset</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>aAcc</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>mIoU</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>mAcc</t>
-        </is>
+      <c r="A1" t="str">
+        <v>Model</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Dataset</v>
+      </c>
+      <c r="C1" t="str">
+        <v>aAcc</v>
+      </c>
+      <c r="D1" t="str">
+        <v>mIoU</v>
+      </c>
+      <c r="E1" t="str">
+        <v>mAcc</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>SAM3</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>VDDDataset</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>75.11000061035156</v>
-      </c>
-      <c r="D2" t="n">
-        <v>64.45999908447266</v>
-      </c>
-      <c r="E2" t="n">
-        <v>82.65000152587891</v>
+      <c r="A2" t="str">
+        <v>SAM3</v>
+      </c>
+      <c r="B2" t="str">
+        <v>VDDDataset</v>
+      </c>
+      <c r="C2" t="str">
+        <v>75.11000061</v>
+      </c>
+      <c r="D2" t="str">
+        <v>64.45999908</v>
+      </c>
+      <c r="E2" t="str">
+        <v>82.65000153</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>SAM3</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>UDD5Dataset</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>87.12000274658203</v>
-      </c>
-      <c r="D3" t="n">
-        <v>71.61000061035156</v>
-      </c>
-      <c r="E3" t="n">
-        <v>83.08000183105469</v>
+      <c r="A3" t="str">
+        <v>SAM3</v>
+      </c>
+      <c r="B3" t="str">
+        <v>UDD5Dataset</v>
+      </c>
+      <c r="C3" t="str">
+        <v>87.12000275</v>
+      </c>
+      <c r="D3" t="str">
+        <v>71.61000061</v>
+      </c>
+      <c r="E3" t="str">
+        <v>83.08000183</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>SAM3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>LoveDADataset</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>63.81000137329102</v>
-      </c>
-      <c r="D4" t="n">
-        <v>47.38999938964844</v>
-      </c>
-      <c r="E4" t="n">
-        <v>62.0099983215332</v>
+      <c r="A4" t="str">
+        <v>SAM3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>LoveDADataset</v>
+      </c>
+      <c r="C4" t="str">
+        <v>63.81000137</v>
+      </c>
+      <c r="D4" t="str">
+        <v>47.38999939</v>
+      </c>
+      <c r="E4" t="str">
+        <v>62.00999832</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>SAM3</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>ISPRSDataset</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>81.26999664306641</v>
-      </c>
-      <c r="D5" t="n">
-        <v>60.7599983215332</v>
-      </c>
-      <c r="E5" t="n">
-        <v>78.44000244140625</v>
+      <c r="A5" t="str">
+        <v>SAM3</v>
+      </c>
+      <c r="B5" t="str">
+        <v>ISPRSDataset</v>
+      </c>
+      <c r="C5" t="str">
+        <v>81.26999664</v>
+      </c>
+      <c r="D5" t="str">
+        <v>60.75999832</v>
+      </c>
+      <c r="E5" t="str">
+        <v>78.44000244</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>SAM3</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>PotsdamDataset</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>77.19000244140625</v>
-      </c>
-      <c r="D6" t="n">
-        <v>57.81999969482422</v>
-      </c>
-      <c r="E6" t="n">
-        <v>72.16000366210938</v>
+      <c r="A6" t="str">
+        <v>SAM3</v>
+      </c>
+      <c r="B6" t="str">
+        <v>PotsdamDataset</v>
+      </c>
+      <c r="C6" t="str">
+        <v>77.19000244</v>
+      </c>
+      <c r="D6" t="str">
+        <v>57.81999969</v>
+      </c>
+      <c r="E6" t="str">
+        <v>72.16000366</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SAM3</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>OpenEarthMapDataset</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>65.12000274658203</v>
-      </c>
-      <c r="D7" t="n">
-        <v>44.18999862670898</v>
-      </c>
-      <c r="E7" t="n">
-        <v>68.52999877929688</v>
+      <c r="A7" t="str">
+        <v>SAM3</v>
+      </c>
+      <c r="B7" t="str">
+        <v>OpenEarthMapDataset</v>
+      </c>
+      <c r="C7" t="str">
+        <v>65.12000275</v>
+      </c>
+      <c r="D7" t="str">
+        <v>44.18999863</v>
+      </c>
+      <c r="E7" t="str">
+        <v>68.52999878</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>SAM3</v>
+      </c>
+      <c r="B8" t="str">
+        <v>iSAIDDataset</v>
+      </c>
+      <c r="C8" t="str">
+        <v>95.87999725341797</v>
+      </c>
+      <c r="D8" t="str">
+        <v>27.420000076293945</v>
+      </c>
+      <c r="E8" t="str">
+        <v>45.9900016784668</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E8"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/results0.xlsx
+++ b/results0.xlsx
@@ -1,52 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Sheet" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -65,13 +42,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -396,148 +440,252 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>Model</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Dataset</v>
-      </c>
-      <c r="C1" t="str">
-        <v>aAcc</v>
-      </c>
-      <c r="D1" t="str">
-        <v>mIoU</v>
-      </c>
-      <c r="E1" t="str">
-        <v>mAcc</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>aAcc</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>mIoU</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>mAcc</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>SAM3</v>
-      </c>
-      <c r="B2" t="str">
-        <v>VDDDataset</v>
-      </c>
-      <c r="C2" t="str">
-        <v>75.11000061</v>
-      </c>
-      <c r="D2" t="str">
-        <v>64.45999908</v>
-      </c>
-      <c r="E2" t="str">
-        <v>82.65000153</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SAM3</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>VDDDataset</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>75.11000061</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>64.45999908</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>82.65000153</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>SAM3</v>
-      </c>
-      <c r="B3" t="str">
-        <v>UDD5Dataset</v>
-      </c>
-      <c r="C3" t="str">
-        <v>87.12000275</v>
-      </c>
-      <c r="D3" t="str">
-        <v>71.61000061</v>
-      </c>
-      <c r="E3" t="str">
-        <v>83.08000183</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SAM3</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>UDD5Dataset</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>87.12000275</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>71.61000061</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>83.08000183</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>SAM3</v>
-      </c>
-      <c r="B4" t="str">
-        <v>LoveDADataset</v>
-      </c>
-      <c r="C4" t="str">
-        <v>63.81000137</v>
-      </c>
-      <c r="D4" t="str">
-        <v>47.38999939</v>
-      </c>
-      <c r="E4" t="str">
-        <v>62.00999832</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SAM3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LoveDADataset</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>63.81000137</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>47.38999939</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>62.00999832</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>SAM3</v>
-      </c>
-      <c r="B5" t="str">
-        <v>ISPRSDataset</v>
-      </c>
-      <c r="C5" t="str">
-        <v>81.26999664</v>
-      </c>
-      <c r="D5" t="str">
-        <v>60.75999832</v>
-      </c>
-      <c r="E5" t="str">
-        <v>78.44000244</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SAM3</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ISPRSDataset</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>81.26999664</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>60.75999832</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>78.44000244</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>SAM3</v>
-      </c>
-      <c r="B6" t="str">
-        <v>PotsdamDataset</v>
-      </c>
-      <c r="C6" t="str">
-        <v>77.19000244</v>
-      </c>
-      <c r="D6" t="str">
-        <v>57.81999969</v>
-      </c>
-      <c r="E6" t="str">
-        <v>72.16000366</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SAM3</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PotsdamDataset</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>77.19000244</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>57.81999969</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>72.16000366</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v>SAM3</v>
-      </c>
-      <c r="B7" t="str">
-        <v>OpenEarthMapDataset</v>
-      </c>
-      <c r="C7" t="str">
-        <v>65.12000275</v>
-      </c>
-      <c r="D7" t="str">
-        <v>44.18999863</v>
-      </c>
-      <c r="E7" t="str">
-        <v>68.52999878</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SAM3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>OpenEarthMapDataset</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>65.12000275</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>44.18999863</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>68.52999878</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
-        <v>SAM3</v>
-      </c>
-      <c r="B8" t="str">
-        <v>iSAIDDataset</v>
-      </c>
-      <c r="C8" t="str">
-        <v>95.87999725341797</v>
-      </c>
-      <c r="D8" t="str">
-        <v>27.420000076293945</v>
-      </c>
-      <c r="E8" t="str">
-        <v>45.9900016784668</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SAM3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>iSAIDDataset</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>95.87999725341797</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>27.420000076293945</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>45.9900016784668</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SAM3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DLRSDDataset</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>42.9900016784668</v>
+      </c>
+      <c r="D9" t="n">
+        <v>28.45000076293945</v>
+      </c>
+      <c r="E9" t="n">
+        <v>41.68000030517578</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E8"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results0.xlsx
+++ b/results0.xlsx
@@ -1,24 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr codeName="ThisWorkbook"/>
+  <workbookPr/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
-      <sz val="12"/>
+      <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -29,7 +39,14 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -39,15 +56,30 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -124,10 +156,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -165,71 +197,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -253,50 +285,53 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
                 <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:tint val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
+              <a:shade val="9500"/>
               <a:satMod val="105000"/>
             </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -306,7 +341,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -315,7 +350,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -324,7 +359,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -332,10 +367,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
+              <a:rot rev="0" lon="0" lat="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -364,7 +399,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
+                <a:tint val="20000"/>
                 <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
@@ -377,13 +412,12 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
                 <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
@@ -395,46 +429,7 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
@@ -442,250 +437,404 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Dataset</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>aAcc</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>mIoU</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>mAcc</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>SAM3</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+    <row r="2" ht="18.75" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>SAM3</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>VDDDataset</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>75.11000061</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>64.45999908</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>82.65000153</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>SAM3</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="C2" s="5" t="n">
+        <v>75.11000061</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>64.45999908</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>82.65000153</v>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>SAM3</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>UDD5Dataset</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>87.12000275</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>71.61000061</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>83.08000183</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>SAM3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+      <c r="C3" s="5" t="n">
+        <v>87.12000275</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>71.61000061</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>83.08000183</v>
+      </c>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>SAM3</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>LoveDADataset</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>63.81000137</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>47.38999939</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>62.00999832</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>SAM3</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="C4" s="5" t="n">
+        <v>63.81000137</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>47.38999939</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>62.00999832</v>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>SAM3</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>ISPRSDataset</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>81.26999664</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>60.75999832</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>78.44000244</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>SAM3</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="C5" s="5" t="n">
+        <v>81.26999664</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>60.75999832</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>78.44000244</v>
+      </c>
+    </row>
+    <row r="6" ht="18.75" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>SAM3</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>PotsdamDataset</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>77.19000244</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>57.81999969</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>72.16000366</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SAM3</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
+      <c r="C6" s="5" t="n">
+        <v>77.19000244</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>57.81999969</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>72.16000366</v>
+      </c>
+    </row>
+    <row r="7" ht="18.75" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SAM3</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>OpenEarthMapDataset</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>65.12000275</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>44.18999863</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>68.52999878</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>SAM3</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
+      <c r="C7" s="5" t="n">
+        <v>65.12000275</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>44.18999863</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>68.52999878</v>
+      </c>
+    </row>
+    <row r="8" ht="18.75" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SAM3</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>iSAIDDataset</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>95.87999725341797</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>27.420000076293945</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>45.9900016784668</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>SAM3</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+      <c r="C8" s="5" t="n">
+        <v>95.87999725341797</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>27.42000007629395</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>45.9900016784668</v>
+      </c>
+    </row>
+    <row r="9" ht="18.75" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SAM3</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>DLRSDDataset</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="3" t="n">
         <v>42.9900016784668</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3" t="n">
         <v>28.45000076293945</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="3" t="n">
         <v>41.68000030517578</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SAM3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DLRSDDataset</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>43.0099983215332</v>
+      </c>
+      <c r="D10" t="n">
+        <v>28.38999938964844</v>
+      </c>
+      <c r="E10" t="n">
+        <v>41.68000030517578</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SAM3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>DLRSDDataset</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>59.29000091552734</v>
+      </c>
+      <c r="D11" t="n">
+        <v>35.84999847412109</v>
+      </c>
+      <c r="E11" t="n">
+        <v>53.22000122070312</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SAM3_SRInput</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>DLRSDDataset</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>58.75</v>
+      </c>
+      <c r="D12" t="n">
+        <v>35.79999923706055</v>
+      </c>
+      <c r="E12" t="n">
+        <v>50.90000152587891</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SAM3_SRInput</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>DLRSDDataset</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>58.88000106811523</v>
+      </c>
+      <c r="D13" t="n">
+        <v>35.9900016784668</v>
+      </c>
+      <c r="E13" t="n">
+        <v>53.04000091552734</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SAM3_SRInput</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DLRSDDataset</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>52.15999984741211</v>
+      </c>
+      <c r="D14" t="n">
+        <v>25.89999961853027</v>
+      </c>
+      <c r="E14" t="n">
+        <v>43.27999877929688</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SAM3_SRInput</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>iSAIDDataset</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>96.58999633789062</v>
+      </c>
+      <c r="D15" t="n">
+        <v>25.23999977111816</v>
+      </c>
+      <c r="E15" t="n">
+        <v>42.02000045776367</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SAM3</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>DLRSDDataset</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>59.29000091552734</v>
+      </c>
+      <c r="D16" t="n">
+        <v>35.84999847412109</v>
+      </c>
+      <c r="E16" t="n">
+        <v>53.22000122070312</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SAM3</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>iSAIDSplitDataset</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>55.0099983215332</v>
+      </c>
+      <c r="D17" t="n">
+        <v>35.59999847412109</v>
+      </c>
+      <c r="E17" t="n">
+        <v>59.38999938964844</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SAM3</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>iSAIDDataset</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>96.40000152587891</v>
+      </c>
+      <c r="D18" t="n">
+        <v>27.61000061035156</v>
+      </c>
+      <c r="E18" t="n">
+        <v>45.56999969482422</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>